--- a/learning_summary.xlsx
+++ b/learning_summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mohsin-Personal\Python-Learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC81A23-F2FD-4B1C-A664-3C1BDC34DE88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B39B935-9928-440A-BFC8-B2468ECA4691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{975AB781-A782-4B7B-AE97-21F5DA85B194}"/>
   </bookViews>
@@ -284,7 +284,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -299,14 +299,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -637,16 +638,16 @@
       </c>
     </row>
     <row r="2" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="7"/>
+      <c r="B2" s="9"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>1</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="7" t="s">
         <v>2</v>
       </c>
     </row>
@@ -654,7 +655,7 @@
       <c r="A4" s="4">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
     </row>
@@ -702,7 +703,7 @@
       <c r="A10" s="4">
         <v>8</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="10" t="s">
         <v>9</v>
       </c>
     </row>
@@ -747,10 +748,10 @@
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="7"/>
+      <c r="B16" s="9"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
@@ -825,16 +826,16 @@
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="7"/>
+      <c r="B26" s="9"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>1</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="6" t="s">
         <v>27</v>
       </c>
     </row>
@@ -842,7 +843,7 @@
       <c r="A28" s="4">
         <v>2</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
     </row>
@@ -850,7 +851,7 @@
       <c r="A29" s="4">
         <v>3</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -858,7 +859,7 @@
       <c r="A30" s="4">
         <v>4</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="6" t="s">
         <v>30</v>
       </c>
     </row>
@@ -866,7 +867,7 @@
       <c r="A31" s="4">
         <v>5</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="6" t="s">
         <v>31</v>
       </c>
     </row>

--- a/learning_summary.xlsx
+++ b/learning_summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mohsin-Personal\Python-Learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B39B935-9928-440A-BFC8-B2468ECA4691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B536CCA-D045-459A-B053-1B4EFF863160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{975AB781-A782-4B7B-AE97-21F5DA85B194}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>S#</t>
   </si>
@@ -181,6 +181,12 @@
       </rPr>
       <t xml:space="preserve"> — deep learning intro</t>
     </r>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>.encode() method left as this is very importance method and need to be practiced more than other methods</t>
   </si>
 </sst>
 </file>
@@ -258,33 +264,33 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
+      <right style="thin">
         <color indexed="64"/>
-      </top>
+      </right>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -294,20 +300,35 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -622,260 +643,297 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A46D576-D8A6-4E32-9F78-96817CBE4889}">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.88671875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.33203125" customWidth="1"/>
+    <col min="1" max="1" width="2.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.33203125" style="13" customWidth="1"/>
+    <col min="3" max="3" width="40.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="C1" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="9"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B2" s="5"/>
+      <c r="C2" s="7"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>1</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="10" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C3" s="1"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>2</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="10" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="11" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>4</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="11" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>5</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="11" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>6</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>7</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>8</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>9</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="11" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>10</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="11" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>11</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="10" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C13" s="1"/>
+    </row>
+    <row r="14" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>12</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="10" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C14" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>13</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="C15" s="1"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="9"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B16" s="5"/>
+      <c r="C16" s="1"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>1</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="11" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C17" s="1"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>2</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="11" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C18" s="1"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>3</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="11" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C19" s="1"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>4</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="11" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C20" s="1"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>5</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="11" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C21" s="1"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>6</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="11" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C22" s="1"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>7</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="11" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C23" s="1"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>8</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C24" s="1"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>9</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="11" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
+      <c r="C25" s="1"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="9"/>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B26" s="5"/>
+      <c r="C26" s="1"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>1</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="12" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C27" s="1"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>2</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="12" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C28" s="1"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>3</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="12" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C29" s="1"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>4</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="12" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C30" s="1"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>5</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="12" t="s">
         <v>31</v>
       </c>
+      <c r="C31" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C1:C2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/learning_summary.xlsx
+++ b/learning_summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mohsin-Personal\Python-Learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B536CCA-D045-459A-B053-1B4EFF863160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C9CFA20-6E78-44C5-A91D-C6CD8A2129C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{975AB781-A782-4B7B-AE97-21F5DA85B194}"/>
   </bookViews>
@@ -232,7 +232,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -315,19 +315,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -647,7 +647,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.33203125" style="13" customWidth="1"/>
+    <col min="2" max="2" width="61.33203125" style="11" customWidth="1"/>
     <col min="3" max="3" width="40.5546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -673,7 +673,7 @@
       <c r="A3" s="4">
         <v>1</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="1"/>
@@ -682,7 +682,7 @@
       <c r="A4" s="4">
         <v>2</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="12" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="1"/>
@@ -691,7 +691,7 @@
       <c r="A5" s="4">
         <v>3</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="9" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="1"/>
@@ -700,7 +700,7 @@
       <c r="A6" s="4">
         <v>4</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="9" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="1"/>
@@ -709,7 +709,7 @@
       <c r="A7" s="4">
         <v>5</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="9" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="1"/>
@@ -718,7 +718,7 @@
       <c r="A8" s="4">
         <v>6</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="9" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="1"/>
@@ -727,7 +727,7 @@
       <c r="A9" s="4">
         <v>7</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="1"/>
@@ -736,7 +736,7 @@
       <c r="A10" s="4">
         <v>8</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="12" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="1"/>
@@ -745,7 +745,7 @@
       <c r="A11" s="4">
         <v>9</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="1"/>
@@ -754,7 +754,7 @@
       <c r="A12" s="4">
         <v>10</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="1"/>
@@ -763,7 +763,7 @@
       <c r="A13" s="4">
         <v>11</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="1"/>
@@ -772,10 +772,10 @@
       <c r="A14" s="4">
         <v>12</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="13" t="s">
         <v>33</v>
       </c>
     </row>
@@ -783,7 +783,7 @@
       <c r="A15" s="4">
         <v>13</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="1"/>
@@ -799,7 +799,7 @@
       <c r="A17" s="4">
         <v>1</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C17" s="1"/>
@@ -808,7 +808,7 @@
       <c r="A18" s="4">
         <v>2</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="9" t="s">
         <v>18</v>
       </c>
       <c r="C18" s="1"/>
@@ -817,7 +817,7 @@
       <c r="A19" s="4">
         <v>3</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="9" t="s">
         <v>19</v>
       </c>
       <c r="C19" s="1"/>
@@ -826,7 +826,7 @@
       <c r="A20" s="4">
         <v>4</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="9" t="s">
         <v>20</v>
       </c>
       <c r="C20" s="1"/>
@@ -835,7 +835,7 @@
       <c r="A21" s="4">
         <v>5</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C21" s="1"/>
@@ -844,7 +844,7 @@
       <c r="A22" s="4">
         <v>6</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="9" t="s">
         <v>22</v>
       </c>
       <c r="C22" s="1"/>
@@ -853,7 +853,7 @@
       <c r="A23" s="4">
         <v>7</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="9" t="s">
         <v>23</v>
       </c>
       <c r="C23" s="1"/>
@@ -862,7 +862,7 @@
       <c r="A24" s="4">
         <v>8</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="9" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="1"/>
@@ -871,7 +871,7 @@
       <c r="A25" s="4">
         <v>9</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="9" t="s">
         <v>25</v>
       </c>
       <c r="C25" s="1"/>
@@ -887,7 +887,7 @@
       <c r="A27" s="4">
         <v>1</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="10" t="s">
         <v>27</v>
       </c>
       <c r="C27" s="1"/>
@@ -896,7 +896,7 @@
       <c r="A28" s="4">
         <v>2</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C28" s="1"/>
@@ -905,7 +905,7 @@
       <c r="A29" s="4">
         <v>3</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="10" t="s">
         <v>29</v>
       </c>
       <c r="C29" s="1"/>
@@ -914,7 +914,7 @@
       <c r="A30" s="4">
         <v>4</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="10" t="s">
         <v>30</v>
       </c>
       <c r="C30" s="1"/>
@@ -923,7 +923,7 @@
       <c r="A31" s="4">
         <v>5</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C31" s="1"/>

--- a/learning_summary.xlsx
+++ b/learning_summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mohsin-Personal\Python-Learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C9CFA20-6E78-44C5-A91D-C6CD8A2129C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{590CDD00-CFF3-4FF2-8372-31E118CFDAEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{975AB781-A782-4B7B-AE97-21F5DA85B194}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="44">
   <si>
     <t>S#</t>
   </si>
@@ -186,7 +186,37 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>.encode() method left as this is very importance method and need to be practiced more than other methods</t>
+    <t>There are a lot of string methods which can be learn day by day. So I'm moving on for now.</t>
+  </si>
+  <si>
+    <t>Bitwise operators are left.</t>
+  </si>
+  <si>
+    <t>Bitwise Conditionals are left.</t>
+  </si>
+  <si>
+    <t>Bitwise loops are left.</t>
+  </si>
+  <si>
+    <t>Bitwise Functions are left.</t>
+  </si>
+  <si>
+    <t>Bitwise scope are left.</t>
+  </si>
+  <si>
+    <t>Bitwise Lists are left.</t>
+  </si>
+  <si>
+    <t>Bitwise tuples are left.</t>
+  </si>
+  <si>
+    <t>Bitwise dictionaries are left.</t>
+  </si>
+  <si>
+    <t>Bitwise sets are left.</t>
+  </si>
+  <si>
+    <t>Bitwise File I/O are left.</t>
   </si>
 </sst>
 </file>
@@ -305,29 +335,29 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -647,7 +677,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.33203125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="61.33203125" style="8" customWidth="1"/>
     <col min="3" max="3" width="40.5546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -655,25 +685,25 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="12" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="7"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="13"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>1</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="9" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="1"/>
@@ -682,7 +712,7 @@
       <c r="A4" s="4">
         <v>2</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="9" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="1"/>
@@ -694,13 +724,15 @@
       <c r="B5" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="1"/>
+      <c r="C5" s="1" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>4</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="6" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="1"/>
@@ -709,7 +741,7 @@
       <c r="A7" s="4">
         <v>5</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="1"/>
@@ -718,7 +750,7 @@
       <c r="A8" s="4">
         <v>6</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="1"/>
@@ -727,7 +759,7 @@
       <c r="A9" s="4">
         <v>7</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="1"/>
@@ -736,7 +768,7 @@
       <c r="A10" s="4">
         <v>8</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="1"/>
@@ -745,7 +777,7 @@
       <c r="A11" s="4">
         <v>9</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="1"/>
@@ -754,7 +786,7 @@
       <c r="A12" s="4">
         <v>10</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="1"/>
@@ -763,19 +795,19 @@
       <c r="A13" s="4">
         <v>11</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>12</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="10" t="s">
         <v>33</v>
       </c>
     </row>
@@ -783,23 +815,23 @@
       <c r="A15" s="4">
         <v>13</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="1"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="5"/>
+      <c r="B16" s="11"/>
       <c r="C16" s="1"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>1</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C17" s="1"/>
@@ -808,7 +840,7 @@
       <c r="A18" s="4">
         <v>2</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C18" s="1"/>
@@ -817,7 +849,7 @@
       <c r="A19" s="4">
         <v>3</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C19" s="1"/>
@@ -826,7 +858,7 @@
       <c r="A20" s="4">
         <v>4</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C20" s="1"/>
@@ -835,7 +867,7 @@
       <c r="A21" s="4">
         <v>5</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C21" s="1"/>
@@ -844,7 +876,7 @@
       <c r="A22" s="4">
         <v>6</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C22" s="1"/>
@@ -853,7 +885,7 @@
       <c r="A23" s="4">
         <v>7</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C23" s="1"/>
@@ -862,7 +894,7 @@
       <c r="A24" s="4">
         <v>8</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="1"/>
@@ -871,23 +903,23 @@
       <c r="A25" s="4">
         <v>9</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C25" s="1"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="5"/>
+      <c r="B26" s="11"/>
       <c r="C26" s="1"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>1</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C27" s="1"/>
@@ -896,7 +928,7 @@
       <c r="A28" s="4">
         <v>2</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="7" t="s">
         <v>28</v>
       </c>
       <c r="C28" s="1"/>
@@ -905,7 +937,7 @@
       <c r="A29" s="4">
         <v>3</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="7" t="s">
         <v>29</v>
       </c>
       <c r="C29" s="1"/>
@@ -914,7 +946,7 @@
       <c r="A30" s="4">
         <v>4</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="7" t="s">
         <v>30</v>
       </c>
       <c r="C30" s="1"/>
@@ -923,7 +955,7 @@
       <c r="A31" s="4">
         <v>5</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C31" s="1"/>

--- a/learning_summary.xlsx
+++ b/learning_summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mohsin-Personal\Python-Learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{590CDD00-CFF3-4FF2-8372-31E118CFDAEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A03DF82B-9680-4EF4-854E-04E0C3BA1D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{975AB781-A782-4B7B-AE97-21F5DA85B194}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>S#</t>
   </si>
@@ -192,38 +192,110 @@
     <t>Bitwise operators are left.</t>
   </si>
   <si>
-    <t>Bitwise Conditionals are left.</t>
-  </si>
-  <si>
-    <t>Bitwise loops are left.</t>
-  </si>
-  <si>
-    <t>Bitwise Functions are left.</t>
-  </si>
-  <si>
-    <t>Bitwise scope are left.</t>
-  </si>
-  <si>
-    <t>Bitwise Lists are left.</t>
-  </si>
-  <si>
-    <t>Bitwise tuples are left.</t>
-  </si>
-  <si>
-    <t>Bitwise dictionaries are left.</t>
-  </si>
-  <si>
-    <t>Bitwise sets are left.</t>
-  </si>
-  <si>
-    <t>Bitwise File I/O are left.</t>
+    <t>Tasks</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Details</t>
+  </si>
+  <si>
+    <t>FizzBuzz</t>
+  </si>
+  <si>
+    <t>Reverse a string</t>
+  </si>
+  <si>
+    <t>Print 1–100, but "Fizz" for multiples of 3, "Buzz" for 5, "FizzBuzz" for both</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Without using </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>[::-1]</t>
+    </r>
+  </si>
+  <si>
+    <t>Count vowels</t>
+  </si>
+  <si>
+    <t>Count vowels in a user-entered sentence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Find duplicates </t>
+  </si>
+  <si>
+    <t>Given a list, find and print all duplicate values</t>
+  </si>
+  <si>
+    <t>Word frequency</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Count how many times each word appears in a sentence (use dictionary)</t>
+  </si>
+  <si>
+    <t>Student grades</t>
+  </si>
+  <si>
+    <t>Store 5 students and their marks in a dict, print pass/fail for each (passing = 50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuple unpacking </t>
+  </si>
+  <si>
+    <t>Store RGB color tuples in a list, print each color's name and values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File word counter </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Write text to a .txt file, read it back, count total words and unique words</t>
+  </si>
+  <si>
+    <t>Contact book</t>
+  </si>
+  <si>
+    <t>Using dict + file I/O:
+Add a contact (name, phone)
+Search contact by name
+Save contacts to a file
+Load contacts when program starts</t>
+  </si>
+  <si>
+    <t>Bitwise operations quiz</t>
+  </si>
+  <si>
+    <t>Generate two random numbers, ask user to calculate AND, OR, XOR manually, verify answer with actual bitwise result</t>
+  </si>
+  <si>
+    <t>Mini inventory system</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Using lists, dicts, and file I/O:
+Add item (name, price, quantity)
+View all items
+Search item by name
+Save/load from file</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Failed</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -246,8 +318,20 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -263,6 +347,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -320,7 +416,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -347,16 +443,47 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -673,33 +800,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A46D576-D8A6-4E32-9F78-96817CBE4889}">
-  <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F31"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="2.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.33203125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="40.5546875" customWidth="1"/>
+    <col min="2" max="2" width="35" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="44.44140625" customWidth="1"/>
+    <col min="6" max="6" width="18.44140625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="2" customFormat="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="17" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="D1" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="2" customFormat="1">
+      <c r="A2" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="13"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B2" s="16"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+    </row>
+    <row r="3" spans="1:6" ht="28.8">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -707,8 +849,17 @@
         <v>2</v>
       </c>
       <c r="C3" s="1"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -716,55 +867,99 @@
         <v>3</v>
       </c>
       <c r="C4" s="1"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="4">
         <v>3</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="11" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="4">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="9" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="1"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6" ht="28.8">
       <c r="A7" s="4">
         <v>5</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="9" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6" ht="28.8">
       <c r="A8" s="4">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="9" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" ht="28.8">
       <c r="A9" s="4">
         <v>7</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6" ht="28.8">
       <c r="A10" s="4">
         <v>8</v>
       </c>
@@ -772,26 +967,47 @@
         <v>9</v>
       </c>
       <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6" ht="86.4">
       <c r="A11" s="4">
         <v>9</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D11" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6" ht="43.2">
       <c r="A12" s="4">
         <v>10</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="1"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6" ht="86.4">
       <c r="A13" s="4">
         <v>11</v>
       </c>
@@ -799,8 +1015,15 @@
         <v>12</v>
       </c>
       <c r="C13" s="1"/>
-    </row>
-    <row r="14" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D13" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6" ht="28.8">
       <c r="A14" s="4">
         <v>12</v>
       </c>
@@ -811,23 +1034,23 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6">
       <c r="A15" s="4">
         <v>13</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="11" t="s">
+    <row r="16" spans="1:6">
+      <c r="A16" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="11"/>
+      <c r="B16" s="16"/>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" s="4">
         <v>1</v>
       </c>
@@ -836,7 +1059,7 @@
       </c>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" s="4">
         <v>2</v>
       </c>
@@ -845,7 +1068,7 @@
       </c>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" s="4">
         <v>3</v>
       </c>
@@ -854,7 +1077,7 @@
       </c>
       <c r="C19" s="1"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20" s="4">
         <v>4</v>
       </c>
@@ -863,7 +1086,7 @@
       </c>
       <c r="C20" s="1"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21" s="4">
         <v>5</v>
       </c>
@@ -872,7 +1095,7 @@
       </c>
       <c r="C21" s="1"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22" s="4">
         <v>6</v>
       </c>
@@ -881,7 +1104,7 @@
       </c>
       <c r="C22" s="1"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23" s="4">
         <v>7</v>
       </c>
@@ -890,7 +1113,7 @@
       </c>
       <c r="C23" s="1"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3">
       <c r="A24" s="4">
         <v>8</v>
       </c>
@@ -899,7 +1122,7 @@
       </c>
       <c r="C24" s="1"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3">
       <c r="A25" s="4">
         <v>9</v>
       </c>
@@ -908,14 +1131,14 @@
       </c>
       <c r="C25" s="1"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="11" t="s">
+    <row r="26" spans="1:3">
+      <c r="A26" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="11"/>
+      <c r="B26" s="16"/>
       <c r="C26" s="1"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3">
       <c r="A27" s="4">
         <v>1</v>
       </c>
@@ -924,7 +1147,7 @@
       </c>
       <c r="C27" s="1"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3">
       <c r="A28" s="4">
         <v>2</v>
       </c>
@@ -933,7 +1156,7 @@
       </c>
       <c r="C28" s="1"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3">
       <c r="A29" s="4">
         <v>3</v>
       </c>
@@ -942,7 +1165,7 @@
       </c>
       <c r="C29" s="1"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3">
       <c r="A30" s="4">
         <v>4</v>
       </c>
@@ -951,7 +1174,7 @@
       </c>
       <c r="C30" s="1"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3">
       <c r="A31" s="4">
         <v>5</v>
       </c>
@@ -961,11 +1184,14 @@
       <c r="C31" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="7">
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
